--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_env_all_sites.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_env_all_sites.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>220.95</v>
+        <v>156.78</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>305.64</v>
+        <v>216.2</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>16.99</v>
+        <v>14.14</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.05 ± 0.48</t>
+          <t>3.11 ± 0.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.47 ± 0.96</t>
+          <t>9.68 ± 1.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.85 ± 0.55</t>
+          <t>3.08 ± 0.46</t>
         </is>
       </c>
     </row>
@@ -535,38 +535,38 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>24.03</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>182.65</v>
+        <v>133.08</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>9.01</v>
+        <v>3.52</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0005***</t>
+          <t>0.0393*</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.64 ± 0.31</t>
+          <t>20.29 ± 0.43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.92 ± 0.87</t>
+          <t>17.84 ± 1.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21.74 ± 0.65</t>
+          <t>20.53 ± 0.30</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.36</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>15.27</v>
+        <v>16.96</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>8.24</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0009***</t>
+          <t>0.1136</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.28 ± 0.10</t>
+          <t>1.31 ± 0.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.48 ± 0.25</t>
+          <t>0.61 ± 0.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.44 ± 0.08</t>
+          <t>1.39 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -625,38 +625,38 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.24</v>
+        <v>42.28</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>56.12</v>
+        <v>604.8200000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>0.52</v>
+        <v>1.36</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.5981</t>
+          <t>0.2677</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.53 ± 0.23</t>
+          <t>2.94 ± 0.71</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.64 ± 0.31</t>
+          <t>6.29 ± 4.30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.17 ± 0.13</t>
+          <t>4.11 ± 0.80</t>
         </is>
       </c>
     </row>
@@ -670,38 +670,38 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.06</v>
+        <v>2.23</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>90.34</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02</v>
+        <v>0.57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.9841</t>
+          <t>0.5727</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.42 ± 0.21</t>
+          <t>9.14 ± 0.28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.33 ± 0.67</t>
+          <t>8.89 ± 0.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>9.38 ± 0.46</t>
+          <t>8.65 ± 0.38</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">

--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_env_all_sites.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_env_all_sites.xlsx
@@ -486,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>156.78</v>
+        <v>17.87</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>216.2</v>
+        <v>31.84</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>14.14</v>
+        <v>15.71</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.11 ± 0.56</t>
+          <t>1.41 ± 0.10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.68 ± 1.34</t>
+          <t>1.40 ± 0.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.08 ± 0.46</t>
+          <t>-0.41 ± 0.43</t>
         </is>
       </c>
     </row>
@@ -531,42 +531,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.03</v>
+        <v>19.8</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>133.08</v>
+        <v>245.32</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>3.52</v>
+        <v>2.26</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0393*</t>
+          <t>0.1138</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.29 ± 0.43</t>
+          <t>2.83 ± 0.32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.84 ± 1.48</t>
+          <t>3.90 ± 0.77</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20.53 ± 0.30</t>
+          <t>4.48 ± 0.69</t>
         </is>
       </c>
     </row>
@@ -576,42 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>16.96</v>
+        <v>29.99</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.1136</t>
+          <t>0.1462</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.31 ± 0.14</t>
+          <t>9.67 ± 0.10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.61 ± 0.54</t>
+          <t>9.20 ± 0.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.39 ± 0.14</t>
+          <t>9.26 ± 0.29</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42.28</v>
+        <v>5.84</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>604.8200000000001</v>
+        <v>308.93</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
-        <v>1.36</v>
+        <v>0.53</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.2677</t>
+          <t>0.5917</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.94 ± 0.71</t>
+          <t>20.09 ± 0.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.29 ± 4.30</t>
+          <t>20.97 ± 0.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4.11 ± 0.80</t>
+          <t>19.88 ± 0.86</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.23</v>
+        <v>0.48</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>76.95999999999999</v>
+        <v>55.57</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>0.57</v>
+        <v>0.24</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.5727</t>
+          <t>0.7875</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.14 ± 0.28</t>
+          <t>1.53 ± 0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.89 ± 0.76</t>
+          <t>1.28 ± 0.15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8.65 ± 0.38</t>
+          <t>1.38 ± 0.22</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">

--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_env_all_sites.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_env_all_sites.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.87</v>
+        <v>17.15</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>31.84</v>
+        <v>28.46</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>15.71</v>
+        <v>14.77</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.41 ± 0.10</t>
+          <t>1.37 ± 0.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.40 ± 0.38</t>
+          <t>1.23 ± 0.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.41 ± 0.43</t>
+          <t>-0.61 ± 0.46</t>
         </is>
       </c>
     </row>
@@ -531,42 +531,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.8</v>
+        <v>39.45</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>245.32</v>
+        <v>268.3</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>2.26</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.1138</t>
+          <t>0.0347*</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.83 ± 0.32</t>
+          <t>19.74 ± 0.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.90 ± 0.77</t>
+          <t>21.76 ± 0.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.48 ± 0.69</t>
+          <t>19.43 ± 0.53</t>
         </is>
       </c>
     </row>
@@ -576,42 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.13</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>29.99</v>
+        <v>159.73</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.1462</t>
+          <t>0.2652</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.67 ± 0.10</t>
+          <t>2.69 ± 0.32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.20 ± 0.40</t>
+          <t>3.03 ± 0.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>9.26 ± 0.29</t>
+          <t>4.10 ± 0.60</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.84</v>
+        <v>1.08</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>308.93</v>
+        <v>29.74</v>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>0.53</v>
+        <v>0.89</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.5917</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20.09 ± 0.37</t>
+          <t>9.65 ± 0.11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.97 ± 0.44</t>
+          <t>9.31 ± 0.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>19.88 ± 0.86</t>
+          <t>9.54 ± 0.26</t>
         </is>
       </c>
     </row>
@@ -670,38 +670,38 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>55.57</v>
+        <v>47.9</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.7875</t>
+          <t>0.6656</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.53 ± 0.16</t>
+          <t>1.50 ± 0.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.28 ± 0.15</t>
+          <t>1.21 ± 0.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.38 ± 0.22</t>
+          <t>1.49 ± 0.15</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">

--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_env_all_sites.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_tests/anova_env_all_sites.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.15</v>
+        <v>17.87</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>28.46</v>
+        <v>31.84</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>14.77</v>
+        <v>15.71</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.37 ± 0.12</t>
+          <t>1.41 ± 0.10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.23 ± 0.23</t>
+          <t>1.40 ± 0.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.61 ± 0.46</t>
+          <t>-0.41 ± 0.43</t>
         </is>
       </c>
     </row>
@@ -531,42 +531,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39.45</v>
+        <v>19.8</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>268.3</v>
+        <v>245.32</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6</v>
+        <v>2.26</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0347*</t>
+          <t>0.1138</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.74 ± 0.42</t>
+          <t>2.83 ± 0.32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21.76 ± 0.61</t>
+          <t>3.90 ± 0.77</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19.43 ± 0.53</t>
+          <t>4.48 ± 0.69</t>
         </is>
       </c>
     </row>
@@ -576,42 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.890000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>159.73</v>
+        <v>29.99</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.2652</t>
+          <t>0.1462</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.69 ± 0.32</t>
+          <t>9.67 ± 0.10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.03 ± 0.49</t>
+          <t>9.20 ± 0.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.10 ± 0.60</t>
+          <t>9.26 ± 0.29</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.08</v>
+        <v>5.84</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>29.74</v>
+        <v>308.93</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.5917</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.65 ± 0.11</t>
+          <t>20.09 ± 0.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.31 ± 0.33</t>
+          <t>20.97 ± 0.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>9.54 ± 0.26</t>
+          <t>19.88 ± 0.86</t>
         </is>
       </c>
     </row>
@@ -670,38 +670,38 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>47.9</v>
+        <v>55.57</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>0.41</v>
+        <v>0.24</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.6656</t>
+          <t>0.7875</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.50 ± 0.19</t>
+          <t>1.53 ± 0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.21 ± 0.14</t>
+          <t>1.28 ± 0.15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.49 ± 0.15</t>
+          <t>1.38 ± 0.22</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
